--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260803.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.89%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.45%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -726,73 +726,73 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>19,587,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -836,29 +836,29 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,587,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -924,29 +924,29 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -968,68 +968,68 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,847,538,544</t>
+          <t>2,169,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,169,000</t>
+          <t>2,815,579,584</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -1144,90 +1144,90 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,384,425,322</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,22 +1239,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>2,323,465,322</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -1276,95 +1276,95 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -1386,24 +1386,24 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1496,51 +1496,51 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1584,156 +1584,156 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,174,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>18,174,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,34 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-31,958,960</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>PFUR_NTD</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>-110,089,104</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
         </is>
       </c>
     </row>
